--- a/public/sap-reporting/expansion-150-downloads/EXT-MM24-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-MM24-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Re49fb50711f9438b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R3585d0069b224ee1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rcf0be771f3b94a70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R9025b4c898b74435"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R3c5021c5e2df469c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R2a3d7831990c4c36"/>
   </x:sheets>
 </x:workbook>
 </file>
